--- a/AAII_Financials/Yearly/RYAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RYAN_YR_FIN.xlsx
@@ -955,7 +955,7 @@
         <v>144000</v>
       </c>
       <c r="E14" s="3">
-        <v>169200</v>
+        <v>187300</v>
       </c>
       <c r="F14" s="3">
         <v>121800</v>
@@ -1156,7 +1156,7 @@
         <v>-15000</v>
       </c>
       <c r="E20" s="3">
-        <v>3800</v>
+        <v>-14300</v>
       </c>
       <c r="F20" s="3">
         <v>8600</v>
@@ -1198,7 +1198,7 @@
         <v>875500</v>
       </c>
       <c r="E21" s="3">
-        <v>695400</v>
+        <v>713500</v>
       </c>
       <c r="F21" s="3">
         <v>534100</v>
@@ -1660,7 +1660,7 @@
         <v>15000</v>
       </c>
       <c r="E32" s="3">
-        <v>-3800</v>
+        <v>14300</v>
       </c>
       <c r="F32" s="3">
         <v>-8600</v>
